--- a/medical_surveys_questionnaires/034_patient_centered_medical_home_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/034_patient_centered_medical_home_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -868,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'medical_surveys_questionnaires',_'label':_'medical_surveys_&amp;_questionnaires',_'value':_'medical_surveys_questionnaires'}</t>
+          <t>medical_surveys_&amp;_questionnaires</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'medical_surveys_questionnaires', 'label': 'Medical Surveys &amp; Questionnaires', 'value': 'medical_surveys_questionnaires'}</t>
+          <t>Medical Surveys &amp; Questionnaires</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'healthcare_surveys',_'label':_'healthcare_surveys',_'value':_'healthcare_surveys'}</t>
+          <t>healthcare_surveys</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'healthcare_surveys', 'label': 'Healthcare Surveys', 'value': 'healthcare_surveys'}</t>
+          <t>Healthcare Surveys</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'others',_'label':_'others',_'value':_'others'}</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'others', 'label': 'Others', 'value': 'others'}</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'034_patient_centered_medical_home_survey--medical_surveys_questionnaires',_'label':_'034_patient_centered_medical_home_survey--medical_surveys_questionnaires',_'value':_'034_patient_centered_medical_home_survey--medical_surveys_questionnaires'}</t>
+          <t>034_patient_centered_medical_home_survey--medical_surveys_questionnaires</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': '034_patient_centered_medical_home_survey--medical_surveys_questionnaires', 'label': '034_patient_centered_medical_home_survey--medical_surveys_questionnaires', 'value': '034_patient_centered_medical_home_survey--medical_surveys_questionnaires'}</t>
+          <t>034 patient centered medical home survey--medical surveys questionnaires</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'034_patient_centered_medical_home_survey--healthcare_surveys',_'label':_'034_patient_centered_medical_home_survey--healthcare_surveys',_'value':_'034_patient_centered_medical_home_survey--healthcare_surveys'}</t>
+          <t>034_patient_centered_medical_home_survey--healthcare_surveys</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': '034_patient_centered_medical_home_survey--healthcare_surveys', 'label': '034_patient_centered_medical_home_survey--healthcare_surveys', 'value': '034_patient_centered_medical_home_survey--healthcare_surveys'}</t>
+          <t>034 patient centered medical home survey--healthcare surveys</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'034_patient_centered_medical_home_survey--others',_'label':_'034_patient_centered_medical_home_survey--others',_'value':_'034_patient_centered_medical_home_survey--others'}</t>
+          <t>034_patient_centered_medical_home_survey--others</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': '034_patient_centered_medical_home_survey--others', 'label': '034_patient_centered_medical_home_survey--others', 'value': '034_patient_centered_medical_home_survey--others'}</t>
+          <t>034 patient centered medical home survey--others</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy',_'label':_'chatjimmy',_'value':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy', 'label': 'chatjimmy', 'value': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'another_tool',_'label':_'another_tool',_'value':_'another_tool'}</t>
+          <t>another_tool</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'another_tool', 'label': 'another_tool', 'value': 'another_tool'}</t>
+          <t>another tool</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'male',_'label':_'male',_'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'male', 'label': 'Male', 'value': 'male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'female',_'label':_'female',_'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'female', 'label': 'Female', 'value': 'female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'other', 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'white',_'label':_'white',_'value':_'white'}</t>
+          <t>white</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'white', 'label': 'White', 'value': 'white'}</t>
+          <t>White</t>
         </is>
       </c>
     </row>
@@ -1105,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'black',_'label':_'black',_'value':_'black'}</t>
+          <t>black</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'black', 'label': 'Black', 'value': 'black'}</t>
+          <t>Black</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'other', 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'not_specified',_'label':_'not_specified',_'value':_'not_specified'}</t>
+          <t>not_specified</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'not_specified', 'label': 'Not Specified', 'value': 'not_specified'}</t>
+          <t>Not Specified</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'not_available',_'label':_'not_available',_'value':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'not_available', 'label': 'Not Available', 'value': 'not_available'}</t>
+          <t>Not Available</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'other', 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'not_specified',_'label':_'not_specified',_'value':_'not_specified'}</t>
+          <t>not_specified</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'not_specified', 'label': 'Not Specified', 'value': 'not_specified'}</t>
+          <t>Not Specified</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'english',_'label':_'english',_'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'english', 'label': 'English', 'value': 'english'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'not_available',_'label':_'not_available',_'value':_'not_available'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'not_available', 'label': 'Not Available', 'value': 'not_available'}</t>
+          <t>Not Available</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'other', 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'spanish',_'label':_'spanish',_'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'spanish', 'label': 'Spanish', 'value': 'spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'chinese',_'label':_'chinese',_'value':_'chinese'}</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'chinese', 'label': 'Chinese', 'value': 'chinese'}</t>
+          <t>Chinese</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'french',_'label':_'french',_'value':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'french', 'label': 'French', 'value': 'french'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'arabic',_'label':_'arabic',_'value':_'arabic'}</t>
+          <t>arabic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'arabic', 'label': 'Arabic', 'value': 'arabic'}</t>
+          <t>Arabic</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'hindi',_'label':_'hindi',_'value':_'hindi'}</t>
+          <t>hindi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'hindi', 'label': 'Hindi', 'value': 'hindi'}</t>
+          <t>Hindi</t>
         </is>
       </c>
     </row>
@@ -1343,29 +1343,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'korean',_'label':_'korean',_'value':_'korean'}</t>
+          <t>korean</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'korean', 'label': 'Korean', 'value': 'korean'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>patient_language_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'id':_11,_'name':_'other',_'label':_'other',_'value':_'other'}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'id': 11, 'name': 'other', 'label': 'Other', 'value': 'other'}</t>
+          <t>Korean</t>
         </is>
       </c>
     </row>
